--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121782835</v>
+        <v>121782837</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597361</v>
+        <v>597230</v>
       </c>
       <c r="R2" t="n">
-        <v>7176875</v>
+        <v>7176936</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121782834</v>
+        <v>121782841</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597399</v>
+        <v>597160</v>
       </c>
       <c r="R3" t="n">
-        <v>7176869</v>
+        <v>7177021</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121782833</v>
+        <v>121782840</v>
       </c>
       <c r="B4" t="n">
-        <v>57785</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597397</v>
+        <v>597175</v>
       </c>
       <c r="R4" t="n">
-        <v>7176868</v>
+        <v>7176986</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782832</v>
+        <v>121782831</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597438</v>
+        <v>596916</v>
       </c>
       <c r="R5" t="n">
-        <v>7176878</v>
+        <v>7176820</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121782841</v>
+        <v>121782834</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597160</v>
+        <v>597399</v>
       </c>
       <c r="R6" t="n">
-        <v>7177021</v>
+        <v>7176869</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121782831</v>
+        <v>121782832</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596916</v>
+        <v>597438</v>
       </c>
       <c r="R7" t="n">
-        <v>7176820</v>
+        <v>7176878</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121782840</v>
+        <v>121782835</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,34 +1368,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597175</v>
+        <v>597361</v>
       </c>
       <c r="R8" t="n">
-        <v>7176986</v>
+        <v>7176875</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121782836</v>
+        <v>121782839</v>
       </c>
       <c r="B9" t="n">
-        <v>82400</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,34 +1485,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597233</v>
+        <v>597175</v>
       </c>
       <c r="R9" t="n">
-        <v>7176930</v>
+        <v>7176985</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121782838</v>
+        <v>121782833</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>57785</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,34 +1602,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597231</v>
+        <v>597397</v>
       </c>
       <c r="R10" t="n">
-        <v>7176934</v>
+        <v>7176868</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121782837</v>
+        <v>121782836</v>
       </c>
       <c r="B11" t="n">
-        <v>74722</v>
+        <v>82400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597230</v>
+        <v>597233</v>
       </c>
       <c r="R11" t="n">
-        <v>7176936</v>
+        <v>7176930</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1810,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121782839</v>
+        <v>121782838</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597175</v>
+        <v>597231</v>
       </c>
       <c r="R12" t="n">
-        <v>7176985</v>
+        <v>7176934</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121782837</v>
+        <v>121782838</v>
       </c>
       <c r="B2" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597230</v>
+        <v>597231</v>
       </c>
       <c r="R2" t="n">
-        <v>7176936</v>
+        <v>7176934</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121782841</v>
+        <v>121782837</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597160</v>
+        <v>597230</v>
       </c>
       <c r="R3" t="n">
-        <v>7177021</v>
+        <v>7176936</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121782840</v>
+        <v>121782834</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597175</v>
+        <v>597399</v>
       </c>
       <c r="R4" t="n">
-        <v>7176986</v>
+        <v>7176869</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782831</v>
+        <v>121782835</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1047,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596916</v>
+        <v>597361</v>
       </c>
       <c r="R5" t="n">
-        <v>7176820</v>
+        <v>7176875</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121782834</v>
+        <v>121782839</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597399</v>
+        <v>597175</v>
       </c>
       <c r="R6" t="n">
-        <v>7176869</v>
+        <v>7176985</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121782832</v>
+        <v>121782833</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>57785</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597438</v>
+        <v>597397</v>
       </c>
       <c r="R7" t="n">
-        <v>7176878</v>
+        <v>7176868</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121782835</v>
+        <v>121782841</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,39 +1378,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597361</v>
+        <v>597160</v>
       </c>
       <c r="R8" t="n">
-        <v>7176875</v>
+        <v>7177021</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121782839</v>
+        <v>121782840</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,29 +1490,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
@@ -1517,7 +1517,7 @@
         <v>597175</v>
       </c>
       <c r="R9" t="n">
-        <v>7176985</v>
+        <v>7176986</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121782833</v>
+        <v>121782831</v>
       </c>
       <c r="B10" t="n">
-        <v>57785</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,27 +1602,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597397</v>
+        <v>596916</v>
       </c>
       <c r="R10" t="n">
-        <v>7176868</v>
+        <v>7176820</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121782838</v>
+        <v>121782832</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597231</v>
+        <v>597438</v>
       </c>
       <c r="R12" t="n">
-        <v>7176934</v>
+        <v>7176878</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121782838</v>
+        <v>121782832</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597231</v>
+        <v>597438</v>
       </c>
       <c r="R2" t="n">
-        <v>7176934</v>
+        <v>7176878</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121782837</v>
+        <v>121782833</v>
       </c>
       <c r="B3" t="n">
-        <v>74722</v>
+        <v>57785</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597230</v>
+        <v>597397</v>
       </c>
       <c r="R3" t="n">
-        <v>7176936</v>
+        <v>7176868</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121782834</v>
+        <v>121782831</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597399</v>
+        <v>596916</v>
       </c>
       <c r="R4" t="n">
-        <v>7176869</v>
+        <v>7176820</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782835</v>
+        <v>121782836</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597361</v>
+        <v>597233</v>
       </c>
       <c r="R5" t="n">
-        <v>7176875</v>
+        <v>7176930</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121782839</v>
+        <v>121782835</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,16 +1149,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,7 +1169,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597175</v>
+        <v>597361</v>
       </c>
       <c r="R6" t="n">
-        <v>7176985</v>
+        <v>7176875</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121782833</v>
+        <v>121782834</v>
       </c>
       <c r="B7" t="n">
-        <v>57785</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597397</v>
+        <v>597399</v>
       </c>
       <c r="R7" t="n">
-        <v>7176868</v>
+        <v>7176869</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121782841</v>
+        <v>121782839</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,34 +1378,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597160</v>
+        <v>597175</v>
       </c>
       <c r="R8" t="n">
-        <v>7177021</v>
+        <v>7176985</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121782840</v>
+        <v>121782837</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597175</v>
+        <v>597230</v>
       </c>
       <c r="R9" t="n">
-        <v>7176986</v>
+        <v>7176936</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121782831</v>
+        <v>121782840</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,39 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596916</v>
+        <v>597175</v>
       </c>
       <c r="R10" t="n">
-        <v>7176820</v>
+        <v>7176986</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121782836</v>
+        <v>121782841</v>
       </c>
       <c r="B11" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597233</v>
+        <v>597160</v>
       </c>
       <c r="R11" t="n">
-        <v>7176930</v>
+        <v>7177021</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121782832</v>
+        <v>121782838</v>
       </c>
       <c r="B12" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597438</v>
+        <v>597231</v>
       </c>
       <c r="R12" t="n">
-        <v>7176878</v>
+        <v>7176934</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121782832</v>
+        <v>121782833</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>57785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597438</v>
+        <v>597397</v>
       </c>
       <c r="R2" t="n">
-        <v>7176878</v>
+        <v>7176868</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121782833</v>
+        <v>121782832</v>
       </c>
       <c r="B3" t="n">
-        <v>57785</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597397</v>
+        <v>597438</v>
       </c>
       <c r="R3" t="n">
-        <v>7176868</v>
+        <v>7176878</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782836</v>
+        <v>121782835</v>
       </c>
       <c r="B5" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597233</v>
+        <v>597361</v>
       </c>
       <c r="R5" t="n">
-        <v>7176930</v>
+        <v>7176875</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121782835</v>
+        <v>121782836</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597361</v>
+        <v>597233</v>
       </c>
       <c r="R6" t="n">
-        <v>7176875</v>
+        <v>7176930</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121782834</v>
+        <v>121782839</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597399</v>
+        <v>597175</v>
       </c>
       <c r="R7" t="n">
-        <v>7176869</v>
+        <v>7176985</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121782839</v>
+        <v>121782838</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,39 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597175</v>
+        <v>597231</v>
       </c>
       <c r="R8" t="n">
-        <v>7176985</v>
+        <v>7176934</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121782837</v>
+        <v>121782841</v>
       </c>
       <c r="B9" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597230</v>
+        <v>597160</v>
       </c>
       <c r="R9" t="n">
-        <v>7176936</v>
+        <v>7177021</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121782841</v>
+        <v>121782834</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597160</v>
+        <v>597399</v>
       </c>
       <c r="R11" t="n">
-        <v>7177021</v>
+        <v>7176869</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121782838</v>
+        <v>121782837</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597231</v>
+        <v>597230</v>
       </c>
       <c r="R12" t="n">
-        <v>7176934</v>
+        <v>7176936</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121782833</v>
+        <v>121782832</v>
       </c>
       <c r="B2" t="n">
-        <v>57785</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597397</v>
+        <v>597438</v>
       </c>
       <c r="R2" t="n">
-        <v>7176868</v>
+        <v>7176878</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121782832</v>
+        <v>121782831</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597438</v>
+        <v>596916</v>
       </c>
       <c r="R3" t="n">
-        <v>7176878</v>
+        <v>7176820</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121782831</v>
+        <v>121782839</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596916</v>
+        <v>597175</v>
       </c>
       <c r="R4" t="n">
-        <v>7176820</v>
+        <v>7176985</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782835</v>
+        <v>121782837</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597361</v>
+        <v>597230</v>
       </c>
       <c r="R5" t="n">
-        <v>7176875</v>
+        <v>7176936</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121782836</v>
+        <v>121782838</v>
       </c>
       <c r="B6" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597233</v>
+        <v>597231</v>
       </c>
       <c r="R6" t="n">
-        <v>7176930</v>
+        <v>7176934</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121782839</v>
+        <v>121782834</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597175</v>
+        <v>597399</v>
       </c>
       <c r="R7" t="n">
-        <v>7176985</v>
+        <v>7176869</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121782838</v>
+        <v>121782835</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1373,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597231</v>
+        <v>597361</v>
       </c>
       <c r="R8" t="n">
-        <v>7176934</v>
+        <v>7176875</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1591,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121782840</v>
+        <v>121782833</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>57785</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,34 +1602,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597175</v>
+        <v>597397</v>
       </c>
       <c r="R10" t="n">
-        <v>7176986</v>
+        <v>7176868</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121782834</v>
+        <v>121782836</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597399</v>
+        <v>597233</v>
       </c>
       <c r="R11" t="n">
-        <v>7176869</v>
+        <v>7176930</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121782837</v>
+        <v>121782840</v>
       </c>
       <c r="B12" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597230</v>
+        <v>597175</v>
       </c>
       <c r="R12" t="n">
-        <v>7176936</v>
+        <v>7176986</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121782832</v>
+        <v>121782839</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597438</v>
+        <v>597175</v>
       </c>
       <c r="R2" t="n">
-        <v>7176878</v>
+        <v>7176985</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121782831</v>
+        <v>121782838</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596916</v>
+        <v>597231</v>
       </c>
       <c r="R3" t="n">
-        <v>7176820</v>
+        <v>7176934</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121782839</v>
+        <v>121782841</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597175</v>
+        <v>597160</v>
       </c>
       <c r="R4" t="n">
-        <v>7176985</v>
+        <v>7177021</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782837</v>
+        <v>121782832</v>
       </c>
       <c r="B5" t="n">
-        <v>74722</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597230</v>
+        <v>597438</v>
       </c>
       <c r="R5" t="n">
-        <v>7176936</v>
+        <v>7176878</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121782838</v>
+        <v>121782834</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597231</v>
+        <v>597399</v>
       </c>
       <c r="R6" t="n">
-        <v>7176934</v>
+        <v>7176869</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121782834</v>
+        <v>121782835</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597399</v>
+        <v>597361</v>
       </c>
       <c r="R7" t="n">
-        <v>7176869</v>
+        <v>7176875</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121782835</v>
+        <v>121782836</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597361</v>
+        <v>597233</v>
       </c>
       <c r="R8" t="n">
-        <v>7176875</v>
+        <v>7176930</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121782841</v>
+        <v>121782840</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1514,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597160</v>
+        <v>597175</v>
       </c>
       <c r="R9" t="n">
-        <v>7177021</v>
+        <v>7176986</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121782833</v>
+        <v>121782831</v>
       </c>
       <c r="B10" t="n">
-        <v>57785</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,27 +1597,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1631,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597397</v>
+        <v>596916</v>
       </c>
       <c r="R10" t="n">
-        <v>7176868</v>
+        <v>7176820</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121782836</v>
+        <v>121782833</v>
       </c>
       <c r="B11" t="n">
-        <v>82400</v>
+        <v>57785</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1714,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597233</v>
+        <v>597397</v>
       </c>
       <c r="R11" t="n">
-        <v>7176930</v>
+        <v>7176868</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121782840</v>
+        <v>121782837</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597175</v>
+        <v>597230</v>
       </c>
       <c r="R12" t="n">
-        <v>7176986</v>
+        <v>7176936</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782832</v>
+        <v>121782834</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597438</v>
+        <v>597399</v>
       </c>
       <c r="R5" t="n">
-        <v>7176878</v>
+        <v>7176869</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121782834</v>
+        <v>121782832</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597399</v>
+        <v>597438</v>
       </c>
       <c r="R6" t="n">
-        <v>7176869</v>
+        <v>7176878</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121782839</v>
+        <v>121782837</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>74735</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597175</v>
+        <v>597230</v>
       </c>
       <c r="R2" t="n">
-        <v>7176985</v>
+        <v>7176936</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121782838</v>
+        <v>121782834</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597231</v>
+        <v>597399</v>
       </c>
       <c r="R3" t="n">
-        <v>7176934</v>
+        <v>7176869</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121782841</v>
+        <v>121782839</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57381</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597160</v>
+        <v>597175</v>
       </c>
       <c r="R4" t="n">
-        <v>7177021</v>
+        <v>7176985</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782834</v>
+        <v>121782833</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57793</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597399</v>
+        <v>597397</v>
       </c>
       <c r="R5" t="n">
-        <v>7176869</v>
+        <v>7176868</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121782832</v>
+        <v>121782836</v>
       </c>
       <c r="B6" t="n">
-        <v>90746</v>
+        <v>82414</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597438</v>
+        <v>597233</v>
       </c>
       <c r="R6" t="n">
-        <v>7176878</v>
+        <v>7176930</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1248,7 @@
         <v>121782835</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121782836</v>
+        <v>121782840</v>
       </c>
       <c r="B8" t="n">
-        <v>82400</v>
+        <v>78629</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597233</v>
+        <v>597175</v>
       </c>
       <c r="R8" t="n">
-        <v>7176930</v>
+        <v>7176986</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121782840</v>
+        <v>121782841</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597175</v>
+        <v>597160</v>
       </c>
       <c r="R9" t="n">
-        <v>7176986</v>
+        <v>7177021</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,7 +1589,7 @@
         <v>121782831</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1698,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121782833</v>
+        <v>121782838</v>
       </c>
       <c r="B11" t="n">
-        <v>57785</v>
+        <v>78629</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,39 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597397</v>
+        <v>597231</v>
       </c>
       <c r="R11" t="n">
-        <v>7176868</v>
+        <v>7176934</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121782837</v>
+        <v>121782832</v>
       </c>
       <c r="B12" t="n">
-        <v>74722</v>
+        <v>90760</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597230</v>
+        <v>597438</v>
       </c>
       <c r="R12" t="n">
-        <v>7176936</v>
+        <v>7176878</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121782841</v>
+        <v>121782831</v>
       </c>
       <c r="B9" t="n">
-        <v>78629</v>
+        <v>57365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,34 +1490,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597160</v>
+        <v>596916</v>
       </c>
       <c r="R9" t="n">
-        <v>7177021</v>
+        <v>7176820</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121782831</v>
+        <v>121782841</v>
       </c>
       <c r="B10" t="n">
-        <v>57365</v>
+        <v>78629</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,39 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596916</v>
+        <v>597160</v>
       </c>
       <c r="R10" t="n">
-        <v>7176820</v>
+        <v>7177021</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121782837</v>
+        <v>121782834</v>
       </c>
       <c r="B2" t="n">
-        <v>74735</v>
+        <v>78631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597230</v>
+        <v>597399</v>
       </c>
       <c r="R2" t="n">
-        <v>7176936</v>
+        <v>7176869</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121782834</v>
+        <v>121782836</v>
       </c>
       <c r="B3" t="n">
-        <v>78629</v>
+        <v>82416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597399</v>
+        <v>597233</v>
       </c>
       <c r="R3" t="n">
-        <v>7176869</v>
+        <v>7176930</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121782839</v>
+        <v>121782833</v>
       </c>
       <c r="B4" t="n">
-        <v>57381</v>
+        <v>57793</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,27 +915,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597175</v>
+        <v>597397</v>
       </c>
       <c r="R4" t="n">
-        <v>7176985</v>
+        <v>7176868</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782833</v>
+        <v>121782838</v>
       </c>
       <c r="B5" t="n">
-        <v>57793</v>
+        <v>78631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597397</v>
+        <v>597231</v>
       </c>
       <c r="R5" t="n">
-        <v>7176868</v>
+        <v>7176934</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121782836</v>
+        <v>121782837</v>
       </c>
       <c r="B6" t="n">
-        <v>82414</v>
+        <v>74737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597233</v>
+        <v>597230</v>
       </c>
       <c r="R6" t="n">
-        <v>7176930</v>
+        <v>7176936</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1245,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121782835</v>
+        <v>121782831</v>
       </c>
       <c r="B7" t="n">
         <v>57365</v>
@@ -1281,7 +1276,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1290,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597361</v>
+        <v>596916</v>
       </c>
       <c r="R7" t="n">
-        <v>7176875</v>
+        <v>7176820</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1360,7 @@
         <v>121782840</v>
       </c>
       <c r="B8" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1474,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121782831</v>
+        <v>121782839</v>
       </c>
       <c r="B9" t="n">
-        <v>57365</v>
+        <v>57381</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,16 +1485,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1519,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596916</v>
+        <v>597175</v>
       </c>
       <c r="R9" t="n">
-        <v>7176820</v>
+        <v>7176985</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,7 +1589,7 @@
         <v>121782841</v>
       </c>
       <c r="B10" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1703,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121782838</v>
+        <v>121782835</v>
       </c>
       <c r="B11" t="n">
-        <v>78629</v>
+        <v>57365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1714,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597231</v>
+        <v>597361</v>
       </c>
       <c r="R11" t="n">
-        <v>7176934</v>
+        <v>7176875</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1818,7 @@
         <v>121782832</v>
       </c>
       <c r="B12" t="n">
-        <v>90760</v>
+        <v>90762</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121782834</v>
+        <v>121782838</v>
       </c>
       <c r="B2" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597399</v>
+        <v>597231</v>
       </c>
       <c r="R2" t="n">
-        <v>7176869</v>
+        <v>7176934</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121782836</v>
+        <v>121782831</v>
       </c>
       <c r="B3" t="n">
-        <v>82416</v>
+        <v>57365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597233</v>
+        <v>596916</v>
       </c>
       <c r="R3" t="n">
-        <v>7176930</v>
+        <v>7176820</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121782833</v>
+        <v>121782841</v>
       </c>
       <c r="B4" t="n">
-        <v>57793</v>
+        <v>78632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597397</v>
+        <v>597160</v>
       </c>
       <c r="R4" t="n">
-        <v>7176868</v>
+        <v>7177021</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782838</v>
+        <v>121782837</v>
       </c>
       <c r="B5" t="n">
-        <v>78631</v>
+        <v>74737</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597231</v>
+        <v>597230</v>
       </c>
       <c r="R5" t="n">
-        <v>7176934</v>
+        <v>7176936</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121782837</v>
+        <v>121782834</v>
       </c>
       <c r="B6" t="n">
-        <v>74737</v>
+        <v>78632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597230</v>
+        <v>597399</v>
       </c>
       <c r="R6" t="n">
-        <v>7176936</v>
+        <v>7176869</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121782831</v>
+        <v>121782836</v>
       </c>
       <c r="B7" t="n">
-        <v>57365</v>
+        <v>82417</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596916</v>
+        <v>597233</v>
       </c>
       <c r="R7" t="n">
-        <v>7176820</v>
+        <v>7176930</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121782840</v>
+        <v>121782833</v>
       </c>
       <c r="B8" t="n">
-        <v>78631</v>
+        <v>57793</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1368,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597175</v>
+        <v>597397</v>
       </c>
       <c r="R8" t="n">
-        <v>7176986</v>
+        <v>7176868</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121782839</v>
+        <v>121782832</v>
       </c>
       <c r="B9" t="n">
-        <v>57381</v>
+        <v>90763</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,39 +1485,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597175</v>
+        <v>597438</v>
       </c>
       <c r="R9" t="n">
-        <v>7176985</v>
+        <v>7176878</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121782841</v>
+        <v>121782835</v>
       </c>
       <c r="B10" t="n">
-        <v>78631</v>
+        <v>57365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,34 +1597,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597160</v>
+        <v>597361</v>
       </c>
       <c r="R10" t="n">
-        <v>7177021</v>
+        <v>7176875</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121782835</v>
+        <v>121782840</v>
       </c>
       <c r="B11" t="n">
-        <v>57365</v>
+        <v>78632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,39 +1714,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597361</v>
+        <v>597175</v>
       </c>
       <c r="R11" t="n">
-        <v>7176875</v>
+        <v>7176986</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121782832</v>
+        <v>121782839</v>
       </c>
       <c r="B12" t="n">
-        <v>90762</v>
+        <v>57381</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597438</v>
+        <v>597175</v>
       </c>
       <c r="R12" t="n">
-        <v>7176878</v>
+        <v>7176985</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121782838</v>
+        <v>121782831</v>
       </c>
       <c r="B2" t="n">
-        <v>78632</v>
+        <v>57369</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597231</v>
+        <v>596916</v>
       </c>
       <c r="R2" t="n">
-        <v>7176934</v>
+        <v>7176820</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121782831</v>
+        <v>121782838</v>
       </c>
       <c r="B3" t="n">
-        <v>57365</v>
+        <v>78639</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596916</v>
+        <v>597231</v>
       </c>
       <c r="R3" t="n">
-        <v>7176820</v>
+        <v>7176934</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
         <v>121782841</v>
       </c>
       <c r="B4" t="n">
-        <v>78632</v>
+        <v>78639</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782837</v>
+        <v>121782836</v>
       </c>
       <c r="B5" t="n">
-        <v>74737</v>
+        <v>82426</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597230</v>
+        <v>597233</v>
       </c>
       <c r="R5" t="n">
-        <v>7176936</v>
+        <v>7176930</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1131,7 +1131,7 @@
         <v>121782834</v>
       </c>
       <c r="B6" t="n">
-        <v>78632</v>
+        <v>78639</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121782836</v>
+        <v>121782837</v>
       </c>
       <c r="B7" t="n">
-        <v>82417</v>
+        <v>74741</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597233</v>
+        <v>597230</v>
       </c>
       <c r="R7" t="n">
-        <v>7176930</v>
+        <v>7176936</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,7 +1355,7 @@
         <v>121782833</v>
       </c>
       <c r="B8" t="n">
-        <v>57793</v>
+        <v>57797</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121782832</v>
+        <v>121782840</v>
       </c>
       <c r="B9" t="n">
-        <v>90763</v>
+        <v>78639</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597438</v>
+        <v>597175</v>
       </c>
       <c r="R9" t="n">
-        <v>7176878</v>
+        <v>7176986</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121782835</v>
+        <v>121782839</v>
       </c>
       <c r="B10" t="n">
-        <v>57365</v>
+        <v>57385</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1617,7 +1617,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597361</v>
+        <v>597175</v>
       </c>
       <c r="R10" t="n">
-        <v>7176875</v>
+        <v>7176985</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121782840</v>
+        <v>121782832</v>
       </c>
       <c r="B11" t="n">
-        <v>78632</v>
+        <v>90772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597175</v>
+        <v>597438</v>
       </c>
       <c r="R11" t="n">
-        <v>7176986</v>
+        <v>7176878</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121782839</v>
+        <v>121782835</v>
       </c>
       <c r="B12" t="n">
-        <v>57381</v>
+        <v>57369</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1846,7 +1846,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597175</v>
+        <v>597361</v>
       </c>
       <c r="R12" t="n">
-        <v>7176985</v>
+        <v>7176875</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 44354-2024 artfynd.xlsx
+++ b/artfynd/A 44354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121782834</v>
+        <v>121782836</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597399</v>
+        <v>597233</v>
       </c>
       <c r="R2" t="n">
-        <v>7176869</v>
+        <v>7176930</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,19 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121782840</v>
+        <v>121782834</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597175</v>
+        <v>597399</v>
       </c>
       <c r="R3" t="n">
-        <v>7176986</v>
+        <v>7176869</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,55 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121782835</v>
+        <v>121782838</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597361</v>
+        <v>597231</v>
       </c>
       <c r="R4" t="n">
-        <v>7176875</v>
+        <v>7176934</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,19 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121782838</v>
+        <v>121782840</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1056,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597231</v>
+        <v>597175</v>
       </c>
       <c r="R5" t="n">
-        <v>7176934</v>
+        <v>7176986</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121782832</v>
+        <v>121782841</v>
       </c>
       <c r="B6" t="n">
-        <v>90781</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597438</v>
+        <v>597160</v>
       </c>
       <c r="R6" t="n">
-        <v>7176878</v>
+        <v>7177021</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121782831</v>
+        <v>121782837</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,39 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596916</v>
+        <v>597230</v>
       </c>
       <c r="R7" t="n">
-        <v>7176820</v>
+        <v>7176936</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,50 +1317,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121782841</v>
+        <v>121782839</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597160</v>
+        <v>597175</v>
       </c>
       <c r="R8" t="n">
-        <v>7177021</v>
+        <v>7176985</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,15 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121782836</v>
+        <v>121782831</v>
       </c>
       <c r="B9" t="n">
-        <v>82432</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,34 +1440,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597233</v>
+        <v>596916</v>
       </c>
       <c r="R9" t="n">
-        <v>7176930</v>
+        <v>7176820</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,15 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121782837</v>
+        <v>121782835</v>
       </c>
       <c r="B10" t="n">
-        <v>74747</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,34 +1552,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597230</v>
+        <v>597361</v>
       </c>
       <c r="R10" t="n">
-        <v>7176936</v>
+        <v>7176875</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,12 +1656,7 @@
         <v>121782833</v>
       </c>
       <c r="B11" t="n">
-        <v>57803</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,123 +1762,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>121782839</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Björnmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>597175</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7176985</v>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
